--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101739070</v>
+        <v>121476842</v>
       </c>
       <c r="B13" t="n">
-        <v>89832</v>
+        <v>90705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,41 +1914,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dergabäcken, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588667.9478239019</v>
+        <v>588022</v>
       </c>
       <c r="R13" t="n">
-        <v>7274866.282232356</v>
+        <v>7274884</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,22 +1972,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,22 +1992,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101739067</v>
+        <v>121476471</v>
       </c>
       <c r="B14" t="n">
-        <v>90160</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,41 +2016,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>918</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dergabäcken, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588678.381758946</v>
+        <v>588106</v>
       </c>
       <c r="R14" t="n">
-        <v>7274850.450994252</v>
+        <v>7274854</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,22 +2074,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,22 +2094,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101739068</v>
+        <v>101739070</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
+        <v>89832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,25 +2118,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588664.8967106888</v>
+        <v>588667.9478239019</v>
       </c>
       <c r="R15" t="n">
-        <v>7274871.158241054</v>
+        <v>7274866.282232356</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2201,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,10 +2218,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101739069</v>
+        <v>101739067</v>
       </c>
       <c r="B16" t="n">
-        <v>89388</v>
+        <v>90160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,25 +2230,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588662.5540141424</v>
+        <v>588678.381758946</v>
       </c>
       <c r="R16" t="n">
-        <v>7274907.11356595</v>
+        <v>7274850.450994252</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2313,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,6 +2327,230 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>101739068</v>
+      </c>
+      <c r="B17" t="n">
+        <v>89410</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dergabäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>588664.8967106888</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7274871.158241054</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>101739069</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89388</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dergabäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>588662.5540141424</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7274907.11356595</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476842</v>
+        <v>121476471</v>
       </c>
       <c r="B13" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588022</v>
+        <v>588106</v>
       </c>
       <c r="R13" t="n">
-        <v>7274884</v>
+        <v>7274854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476471</v>
+        <v>121476842</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>90706</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588106</v>
+        <v>588022</v>
       </c>
       <c r="R14" t="n">
-        <v>7274854</v>
+        <v>7274884</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476471</v>
+        <v>121476842</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588106</v>
+        <v>588022</v>
       </c>
       <c r="R13" t="n">
-        <v>7274854</v>
+        <v>7274884</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476842</v>
+        <v>121476471</v>
       </c>
       <c r="B14" t="n">
-        <v>90706</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588022</v>
+        <v>588106</v>
       </c>
       <c r="R14" t="n">
-        <v>7274884</v>
+        <v>7274854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476842</v>
+        <v>121476471</v>
       </c>
       <c r="B13" t="n">
-        <v>90709</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588022</v>
+        <v>588106</v>
       </c>
       <c r="R13" t="n">
-        <v>7274884</v>
+        <v>7274854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476471</v>
+        <v>121476842</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>90709</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588106</v>
+        <v>588022</v>
       </c>
       <c r="R14" t="n">
-        <v>7274854</v>
+        <v>7274884</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101739070</v>
+        <v>121532353</v>
       </c>
       <c r="B15" t="n">
-        <v>89832</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,41 +2118,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dergabäcken, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588667.9478239019</v>
+        <v>588105</v>
       </c>
       <c r="R15" t="n">
-        <v>7274866.282232356</v>
+        <v>7274853</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,22 +2180,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,22 +2210,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101739067</v>
+        <v>101739070</v>
       </c>
       <c r="B16" t="n">
-        <v>90160</v>
+        <v>89832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,21 +2238,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>918</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2258,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588678.381758946</v>
+        <v>588667.9478239019</v>
       </c>
       <c r="R16" t="n">
-        <v>7274850.450994252</v>
+        <v>7274866.282232356</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2293,7 +2297,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2307,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,10 +2334,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101739068</v>
+        <v>101739067</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
+        <v>90160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,25 +2346,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588664.8967106888</v>
+        <v>588678.381758946</v>
       </c>
       <c r="R17" t="n">
-        <v>7274871.158241054</v>
+        <v>7274850.450994252</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2405,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2415,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2442,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101739069</v>
+        <v>101739068</v>
       </c>
       <c r="B18" t="n">
-        <v>89388</v>
+        <v>89410</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,21 +2462,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588662.5540141424</v>
+        <v>588664.8967106888</v>
       </c>
       <c r="R18" t="n">
-        <v>7274907.11356595</v>
+        <v>7274871.158241054</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2517,7 +2521,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2527,7 +2531,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,6 +2555,118 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>101739069</v>
+      </c>
+      <c r="B19" t="n">
+        <v>89388</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dergabäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>588662.5540141424</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7274907.11356595</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -1905,7 +1905,7 @@
         <v>121476471</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>121476842</v>
       </c>
       <c r="B14" t="n">
-        <v>90709</v>
+        <v>90715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>121532353</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -1905,7 +1905,7 @@
         <v>121476471</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>121476842</v>
       </c>
       <c r="B14" t="n">
-        <v>90715</v>
+        <v>90716</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>121532353</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476471</v>
+        <v>121476842</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588106</v>
+        <v>588022</v>
       </c>
       <c r="R13" t="n">
-        <v>7274854</v>
+        <v>7274884</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476842</v>
+        <v>121476471</v>
       </c>
       <c r="B14" t="n">
-        <v>90716</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588022</v>
+        <v>588106</v>
       </c>
       <c r="R14" t="n">
-        <v>7274884</v>
+        <v>7274854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476842</v>
+        <v>121476471</v>
       </c>
       <c r="B13" t="n">
-        <v>90716</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588022</v>
+        <v>588106</v>
       </c>
       <c r="R13" t="n">
-        <v>7274884</v>
+        <v>7274854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476471</v>
+        <v>121476842</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>90716</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588106</v>
+        <v>588022</v>
       </c>
       <c r="R14" t="n">
-        <v>7274854</v>
+        <v>7274884</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -1905,7 +1905,7 @@
         <v>121476471</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>121476842</v>
       </c>
       <c r="B14" t="n">
-        <v>90716</v>
+        <v>90724</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>121532353</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 43976-2020 artfynd.xlsx
+++ b/artfynd/A 43976-2020 artfynd.xlsx
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476842</v>
+        <v>121476471</v>
       </c>
       <c r="B13" t="n">
-        <v>90724</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588022</v>
+        <v>588106</v>
       </c>
       <c r="R13" t="n">
-        <v>7274884</v>
+        <v>7274854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476471</v>
+        <v>121476842</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>90724</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588106</v>
+        <v>588022</v>
       </c>
       <c r="R14" t="n">
-        <v>7274854</v>
+        <v>7274884</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
